--- a/evaluation/fiqa/fiqa_deepseek-reasoner_answers.xlsx
+++ b/evaluation/fiqa/fiqa_deepseek-reasoner_answers.xlsx
@@ -8604,6 +8604,15 @@
       <c r="J22" s="4" t="s">
         <v>202</v>
       </c>
+      <c r="K22" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="N22" s="3" t="n">
         <v>1</v>
       </c>
@@ -8639,13 +8648,13 @@
       <c r="J23" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="K23" s="0" t="n">
+      <c r="K23" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="L23" s="0" t="n">
+      <c r="L23" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M23" s="0" t="n">
+      <c r="M23" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N23" s="3" t="n">
@@ -8683,13 +8692,13 @@
       <c r="J24" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="K24" s="0" t="n">
+      <c r="K24" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="L24" s="0" t="n">
+      <c r="L24" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M24" s="0" t="n">
+      <c r="M24" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N24" s="3" t="n">
@@ -8727,13 +8736,13 @@
       <c r="J25" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="K25" s="0" t="n">
+      <c r="K25" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="L25" s="0" t="n">
+      <c r="L25" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M25" s="0" t="n">
+      <c r="M25" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N25" s="3" t="n">
@@ -8771,13 +8780,13 @@
       <c r="J26" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="K26" s="0" t="n">
+      <c r="K26" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="L26" s="0" t="n">
+      <c r="L26" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M26" s="0" t="n">
+      <c r="M26" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N26" s="3" t="n">
@@ -8815,13 +8824,13 @@
       <c r="J27" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="K27" s="0" t="n">
+      <c r="K27" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="L27" s="0" t="n">
+      <c r="L27" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M27" s="0" t="n">
+      <c r="M27" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N27" s="3" t="n">
@@ -8859,13 +8868,13 @@
       <c r="J28" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="K28" s="0" t="n">
+      <c r="K28" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="L28" s="0" t="n">
+      <c r="L28" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M28" s="0" t="n">
+      <c r="M28" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N28" s="3" t="n">
@@ -8903,13 +8912,13 @@
       <c r="J29" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="K29" s="0" t="n">
+      <c r="K29" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="L29" s="0" t="n">
+      <c r="L29" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M29" s="0" t="n">
+      <c r="M29" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N29" s="3" t="n">
@@ -8947,13 +8956,13 @@
       <c r="J30" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="K30" s="0" t="n">
+      <c r="K30" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="L30" s="0" t="n">
+      <c r="L30" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M30" s="0" t="n">
+      <c r="M30" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N30" s="3" t="n">
@@ -8991,13 +9000,13 @@
       <c r="J31" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="K31" s="0" t="n">
+      <c r="K31" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="L31" s="0" t="n">
+      <c r="L31" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M31" s="0" t="n">
+      <c r="M31" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N31" s="3" t="n">
@@ -9035,13 +9044,13 @@
       <c r="J32" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="K32" s="0" t="n">
+      <c r="K32" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="L32" s="0" t="n">
+      <c r="L32" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M32" s="0" t="n">
+      <c r="M32" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N32" s="3" t="n">
@@ -9079,13 +9088,13 @@
       <c r="J33" s="4" t="s">
         <v>301</v>
       </c>
-      <c r="K33" s="0" t="n">
+      <c r="K33" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="L33" s="0" t="n">
+      <c r="L33" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M33" s="0" t="n">
+      <c r="M33" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N33" s="3" t="n">
@@ -9123,13 +9132,13 @@
       <c r="J34" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="K34" s="0" t="n">
+      <c r="K34" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="L34" s="0" t="n">
+      <c r="L34" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M34" s="0" t="n">
+      <c r="M34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N34" s="3" t="n">
@@ -9167,13 +9176,13 @@
       <c r="J35" s="4" t="s">
         <v>319</v>
       </c>
-      <c r="K35" s="0" t="n">
+      <c r="K35" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="L35" s="0" t="n">
+      <c r="L35" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M35" s="0" t="n">
+      <c r="M35" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N35" s="3" t="n">
@@ -9211,13 +9220,13 @@
       <c r="J36" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="K36" s="0" t="n">
+      <c r="K36" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="L36" s="0" t="n">
+      <c r="L36" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M36" s="0" t="n">
+      <c r="M36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N36" s="3" t="n">
@@ -9255,13 +9264,13 @@
       <c r="J37" s="4" t="s">
         <v>337</v>
       </c>
-      <c r="K37" s="0" t="n">
+      <c r="K37" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="L37" s="0" t="n">
+      <c r="L37" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M37" s="0" t="n">
+      <c r="M37" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N37" s="3" t="n">
@@ -9299,13 +9308,13 @@
       <c r="J38" s="4" t="s">
         <v>346</v>
       </c>
-      <c r="K38" s="0" t="n">
+      <c r="K38" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="L38" s="0" t="n">
+      <c r="L38" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M38" s="0" t="n">
+      <c r="M38" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N38" s="3" t="n">
@@ -9343,13 +9352,13 @@
       <c r="J39" s="4" t="s">
         <v>355</v>
       </c>
-      <c r="K39" s="0" t="n">
+      <c r="K39" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="L39" s="0" t="n">
+      <c r="L39" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M39" s="0" t="n">
+      <c r="M39" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N39" s="3" t="n">
@@ -9387,13 +9396,13 @@
       <c r="J40" s="4" t="s">
         <v>364</v>
       </c>
-      <c r="K40" s="0" t="n">
+      <c r="K40" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="L40" s="0" t="n">
+      <c r="L40" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M40" s="0" t="n">
+      <c r="M40" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N40" s="3" t="n">
@@ -9431,13 +9440,13 @@
       <c r="J41" s="4" t="s">
         <v>373</v>
       </c>
-      <c r="K41" s="0" t="n">
+      <c r="K41" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="L41" s="0" t="n">
+      <c r="L41" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M41" s="0" t="n">
+      <c r="M41" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N41" s="3" t="n">
